--- a/sample/職員名簿_サンプル.xlsx
+++ b/sample/職員名簿_サンプル.xlsx
@@ -713,7 +713,11 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>B111-001</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
@@ -760,7 +764,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>30000</v>
@@ -808,7 +812,11 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>B111-002</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -903,7 +911,11 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>B111-003</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
@@ -950,7 +962,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>31000</v>
@@ -998,7 +1010,11 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>B111-004</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
@@ -1093,7 +1109,11 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>B111-005</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
@@ -1140,7 +1160,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>33000</v>
@@ -1188,7 +1208,11 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>B111-006</t>
+        </is>
+      </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
@@ -1283,7 +1307,11 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>B111-007</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
@@ -1330,7 +1358,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>32000</v>
@@ -1378,7 +1406,11 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>B111-008</t>
+        </is>
+      </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
@@ -1473,7 +1505,11 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>B111-009</t>
+        </is>
+      </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -1520,7 +1556,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>34000</v>
@@ -1568,7 +1604,11 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>B111-010</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -1663,7 +1703,11 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>B111-011</t>
+        </is>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -1710,7 +1754,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>35500</v>
@@ -1758,7 +1802,11 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>B111-012</t>
+        </is>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -1853,7 +1901,11 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>B111-013</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
@@ -1900,7 +1952,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>36600</v>
@@ -1948,7 +2000,11 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>B111-014</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
@@ -2043,7 +2099,11 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>B111-015</t>
+        </is>
+      </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
@@ -2090,7 +2150,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>31500</v>
@@ -2138,7 +2198,11 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>B111-016</t>
+        </is>
+      </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
@@ -2233,7 +2297,11 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>B111-017</t>
+        </is>
+      </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
@@ -2280,7 +2348,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>33500</v>
@@ -2328,7 +2396,11 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>B111-018</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
@@ -2423,7 +2495,11 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>B111-019</t>
+        </is>
+      </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
@@ -2470,7 +2546,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>29500</v>
@@ -2518,7 +2594,11 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>B111-020</t>
+        </is>
+      </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
@@ -2613,7 +2693,11 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>B111-021</t>
+        </is>
+      </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
@@ -2660,7 +2744,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>34500</v>
@@ -2708,7 +2792,11 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>B111-022</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
@@ -2803,7 +2891,11 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>B111-023</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
@@ -2850,7 +2942,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>32500</v>
@@ -2898,7 +2990,11 @@
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>B111-024</t>
+        </is>
+      </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
